--- a/Design_calc/buck_converter_design.xlsx
+++ b/Design_calc/buck_converter_design.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Victus\Desktop\AVIONIX-28\Design_calc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52A8C8F0-B31B-441C-9274-277397403204}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D17A66CF-6109-4AF0-BEB3-1C71A12F87BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="360" windowWidth="23256" windowHeight="12456" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="228" yWindow="948" windowWidth="21600" windowHeight="11292" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Buck Design" sheetId="1" r:id="rId1"/>
@@ -164,7 +164,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="32">
   <si>
     <t>Buck Converter Design Calculations</t>
   </si>
@@ -248,6 +248,18 @@
   </si>
   <si>
     <t>worst case</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Input Capacitors </t>
+  </si>
+  <si>
+    <t>c1 = c2 = c3 = 100uf , c4 = 100nf</t>
+  </si>
+  <si>
+    <t>irms rating = 0.25</t>
+  </si>
+  <si>
+    <t>vin_rip = 0.21&lt; 0.5(1%)</t>
   </si>
 </sst>
 </file>
@@ -349,18 +361,17 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -635,42 +646,42 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
+      <c r="B1" s="7"/>
+      <c r="C1" s="7"/>
+      <c r="D1" s="7"/>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A3" s="1" t="s">
+      <c r="A3" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="1"/>
-      <c r="C3" s="1"/>
-      <c r="D3" s="1"/>
+      <c r="B3" s="6"/>
+      <c r="C3" s="6"/>
+      <c r="D3" s="6"/>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A4" s="3" t="s">
+      <c r="A4" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="4">
+      <c r="B4" s="2">
         <v>28</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A5" s="3" t="s">
+      <c r="A5" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="4">
+      <c r="B5" s="2">
         <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A6" s="3" t="s">
+      <c r="A6" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B6" s="4">
+      <c r="B6" s="2">
         <v>0.85</v>
       </c>
       <c r="C6" t="s">
@@ -678,189 +689,209 @@
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A7" s="3" t="s">
+      <c r="A7" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B7" s="4">
+      <c r="B7" s="2">
         <v>12</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A8" s="3" t="s">
+      <c r="A8" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B8" s="4">
+      <c r="B8" s="2">
         <v>24</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A9" s="3" t="s">
+      <c r="A9" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B9" s="4">
+      <c r="B9" s="2">
         <v>1100</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A10" s="3" t="s">
+      <c r="A10" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B10" s="4">
+      <c r="B10" s="2">
         <v>1.6</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A11" s="3" t="s">
+      <c r="A11" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B11" s="4">
+      <c r="B11" s="2">
         <v>1.2</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A12" s="3" t="s">
+      <c r="A12" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B12" s="4">
+      <c r="B12" s="2">
         <v>0.18</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A13" s="3" t="s">
+      <c r="A13" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B13" s="4">
+      <c r="B13" s="2">
         <v>0.5</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A14" s="3" t="s">
+      <c r="A14" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B14" s="4">
+      <c r="B14" s="2">
         <v>100</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A15" s="3" t="s">
+      <c r="A15" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B15" s="4">
+      <c r="B15" s="2">
         <v>13.3</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A17" s="1" t="s">
+      <c r="A17" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="B17" s="1"/>
-      <c r="C17" s="1"/>
-      <c r="D17" s="1"/>
+      <c r="B17" s="6"/>
+      <c r="C17" s="6"/>
+      <c r="D17" s="6"/>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A18" s="5" t="s">
+      <c r="A18" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="B18" s="6">
+      <c r="B18" s="4">
         <f>(B5/B4)*B6</f>
         <v>0.15178571428571427</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A20" s="1" t="s">
+      <c r="A20" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="B20" s="1"/>
-      <c r="C20" s="1"/>
-      <c r="D20" s="1"/>
+      <c r="B20" s="6"/>
+      <c r="C20" s="6"/>
+      <c r="D20" s="6"/>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A21" s="5" t="s">
+      <c r="A21" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="B21" s="6">
+      <c r="B21" s="4">
         <f>((B4-B5)*B18)/((B9*1000)*(B7*0.000001))</f>
         <v>0.26447510822510817</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A22" s="5" t="s">
+      <c r="A22" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="B22" s="6">
+      <c r="B22" s="4">
         <f>((B4-B5)*B18)/((B9*1000)*(B8*0.000001))</f>
         <v>0.13223755411255408</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A24" s="1" t="s">
+      <c r="A24" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="B24" s="1"/>
-      <c r="C24" s="1"/>
-      <c r="D24" s="1"/>
+      <c r="B24" s="6"/>
+      <c r="C24" s="6"/>
+      <c r="D24" s="6"/>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A25" s="5" t="s">
+      <c r="A25" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="B25" s="7">
+      <c r="B25" s="5">
         <f>B10-B12</f>
         <v>1.4200000000000002</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A26" s="5" t="s">
+      <c r="A26" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="B26" s="7">
+      <c r="B26" s="5">
         <f>B11-B12</f>
         <v>1.02</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A27" s="5" t="s">
+      <c r="A27" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="B27" s="7">
+      <c r="B27" s="5">
         <f>B13+B12</f>
         <v>0.67999999999999994</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A28" s="5" t="s">
+      <c r="A28" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="B28" s="7">
+      <c r="B28" s="5">
         <f>B25-B27</f>
         <v>0.74000000000000021</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A29" s="5" t="s">
+      <c r="A29" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="B29" s="7">
+      <c r="B29" s="5">
         <f>B26-B27</f>
         <v>0.34000000000000008</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A31" s="1" t="s">
+      <c r="A31" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="B31" s="1"/>
-      <c r="C31" s="1"/>
-      <c r="D31" s="1"/>
+      <c r="B31" s="6"/>
+      <c r="C31" s="6"/>
+      <c r="D31" s="6"/>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A32" s="8" t="s">
+      <c r="A32" s="3" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="35" ht="22.35" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A33" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="B33" s="6"/>
+      <c r="C33" s="6"/>
+      <c r="D33" s="6"/>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A34" t="s">
+        <v>29</v>
+      </c>
+      <c r="B34" t="s">
+        <v>30</v>
+      </c>
+      <c r="C34" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" ht="22.35" customHeight="1" x14ac:dyDescent="0.3"/>
   </sheetData>
-  <mergeCells count="6">
+  <mergeCells count="7">
+    <mergeCell ref="A33:D33"/>
     <mergeCell ref="A31:D31"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A3:D3"/>

--- a/Design_calc/buck_converter_design.xlsx
+++ b/Design_calc/buck_converter_design.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Victus\Desktop\AVIONIX-28\Design_calc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D17A66CF-6109-4AF0-BEB3-1C71A12F87BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F418995F-F41A-40B6-980F-E7BD78DFDC58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="228" yWindow="948" windowWidth="21600" windowHeight="11292" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1020" yWindow="1044" windowWidth="21600" windowHeight="11292" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Buck Design" sheetId="1" r:id="rId1"/>
@@ -111,19 +111,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B12" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000007000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <rFont val="Arial"/>
-            <family val="2"/>
-          </rPr>
-          <t>Margin/offset subtracted from datasheet current limits</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="B13" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000008000000}">
+    <comment ref="B12" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000008000000}">
       <text>
         <r>
           <rPr>
@@ -164,7 +152,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="34">
   <si>
     <t>Buck Converter Design Calculations</t>
   </si>
@@ -196,9 +184,6 @@
     <t>LS current limit, datasheet (A)</t>
   </si>
   <si>
-    <t>Margin subtracted (A)</t>
-  </si>
-  <si>
     <t>Max load current Iout (A)</t>
   </si>
   <si>
@@ -253,13 +238,22 @@
     <t xml:space="preserve">Input Capacitors </t>
   </si>
   <si>
-    <t>c1 = c2 = c3 = 100uf , c4 = 100nf</t>
-  </si>
-  <si>
-    <t>irms rating = 0.25</t>
-  </si>
-  <si>
-    <t>vin_rip = 0.21&lt; 0.5(1%)</t>
+    <t>0.151D</t>
+  </si>
+  <si>
+    <t>15uH</t>
+  </si>
+  <si>
+    <t xml:space="preserve">with the datasheet min inductance </t>
+  </si>
+  <si>
+    <t>4-0.24&gt; Iout(max)</t>
+  </si>
+  <si>
+    <t>4-0.24&gt;Iout(max)</t>
+  </si>
+  <si>
+    <t>0.74A</t>
   </si>
 </sst>
 </file>
@@ -685,15 +679,15 @@
         <v>0.85</v>
       </c>
       <c r="C6" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B7" s="2">
-        <v>12</v>
+      <c r="B7" s="2" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.3">
@@ -709,7 +703,7 @@
         <v>7</v>
       </c>
       <c r="B9" s="2">
-        <v>1100</v>
+        <v>500</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.3">
@@ -717,7 +711,7 @@
         <v>8</v>
       </c>
       <c r="B10" s="2">
-        <v>1.6</v>
+        <v>3.9</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.3">
@@ -725,7 +719,7 @@
         <v>9</v>
       </c>
       <c r="B11" s="2">
-        <v>1.2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.3">
@@ -733,7 +727,7 @@
         <v>10</v>
       </c>
       <c r="B12" s="2">
-        <v>0.18</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.3">
@@ -741,7 +735,7 @@
         <v>11</v>
       </c>
       <c r="B13" s="2">
-        <v>0.5</v>
+        <v>100</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.3">
@@ -749,20 +743,12 @@
         <v>12</v>
       </c>
       <c r="B14" s="2">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A15" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B15" s="2">
         <v>13.3</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A17" s="6" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B17" s="6"/>
       <c r="C17" s="6"/>
@@ -770,16 +756,15 @@
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A18" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="B18" s="4">
-        <f>(B5/B4)*B6</f>
-        <v>0.15178571428571427</v>
+        <v>14</v>
+      </c>
+      <c r="B18" s="4" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A20" s="6" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B20" s="6"/>
       <c r="C20" s="6"/>
@@ -787,25 +772,24 @@
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A21" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B21" s="4">
-        <f>((B4-B5)*B18)/((B9*1000)*(B7*0.000001))</f>
-        <v>0.26447510822510817</v>
+        <v>0.48</v>
+      </c>
+      <c r="C21" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A22" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="B22" s="4">
-        <f>((B4-B5)*B18)/((B9*1000)*(B8*0.000001))</f>
-        <v>0.13223755411255408</v>
-      </c>
+        <v>17</v>
+      </c>
+      <c r="B22" s="4"/>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A24" s="6" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B24" s="6"/>
       <c r="C24" s="6"/>
@@ -813,52 +797,44 @@
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A25" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="B25" s="5">
-        <f>B10-B12</f>
-        <v>1.4200000000000002</v>
+        <v>19</v>
+      </c>
+      <c r="B25" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A26" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="B26" s="5">
-        <f>B11-B12</f>
-        <v>1.02</v>
+        <v>20</v>
+      </c>
+      <c r="B26" s="5" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A27" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="B27" s="5">
-        <f>B13+B12</f>
-        <v>0.67999999999999994</v>
+        <v>21</v>
+      </c>
+      <c r="B27" s="5"/>
+      <c r="C27" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A28" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="B28" s="5">
-        <f>B25-B27</f>
-        <v>0.74000000000000021</v>
-      </c>
+        <v>22</v>
+      </c>
+      <c r="B28" s="5"/>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A29" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="B29" s="5">
-        <f>B26-B27</f>
-        <v>0.34000000000000008</v>
-      </c>
+        <v>23</v>
+      </c>
+      <c r="B29" s="5"/>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A31" s="6" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B31" s="6"/>
       <c r="C31" s="6"/>
@@ -866,27 +842,16 @@
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A32" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A33" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B33" s="6"/>
       <c r="C33" s="6"/>
       <c r="D33" s="6"/>
-    </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A34" t="s">
-        <v>29</v>
-      </c>
-      <c r="B34" t="s">
-        <v>30</v>
-      </c>
-      <c r="C34" t="s">
-        <v>31</v>
-      </c>
     </row>
     <row r="35" spans="1:4" ht="22.35" customHeight="1" x14ac:dyDescent="0.3"/>
   </sheetData>
